--- a/week-01/Ex4B_more_GTrends.xlsx
+++ b/week-01/Ex4B_more_GTrends.xlsx
@@ -8,35 +8,40 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brandon\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14AFE884-CFF0-477A-BE36-1790A98271AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB20A62E-EC81-4210-A1D7-4CAF3FE346D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{49F1C08D-31FF-4AB3-807B-E395AC2E4217}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{49F1C08D-31FF-4AB3-807B-E395AC2E4217}"/>
   </bookViews>
   <sheets>
-    <sheet name="GTrends_milkshake_hamburger_202" sheetId="1" r:id="rId1"/>
+    <sheet name="by search term" sheetId="1" r:id="rId1"/>
+    <sheet name="by state" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GTrends_milkshake_hamburger_202!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'by search term'!$A$1:$E$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="59">
   <si>
     <t>Region</t>
   </si>
   <si>
-    <t>Milkshake: (2/1/24 - 2/28/25)</t>
-  </si>
-  <si>
-    <t>Hamburger: (2/1/24 - 2/28/25)</t>
-  </si>
-  <si>
-    <t>Breakup: (2/1/24 - 2/28/25)</t>
-  </si>
-  <si>
     <t>North Carolina</t>
   </si>
   <si>
@@ -194,6 +199,21 @@
   </si>
   <si>
     <t>RegionID</t>
+  </si>
+  <si>
+    <t>date range</t>
+  </si>
+  <si>
+    <t>Hamburger</t>
+  </si>
+  <si>
+    <t>Milkshake</t>
+  </si>
+  <si>
+    <t>Breakup</t>
+  </si>
+  <si>
+    <t>(2/1/24 - 2/28/25)</t>
   </si>
 </sst>
 </file>
@@ -336,7 +356,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -519,6 +539,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,10 +709,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1065,7 +1092,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="3" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1073,38 +1100,46 @@
     <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H1" s="2">
         <f>COUNTA(B2:B52)</f>
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1">
         <v>0.64</v>
@@ -1116,12 +1151,12 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1">
         <v>0.72</v>
@@ -1133,12 +1168,12 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1">
         <v>0.67</v>
@@ -1150,12 +1185,12 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1">
         <v>0.67</v>
@@ -1167,12 +1202,12 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C6" s="1">
         <v>0.67</v>
@@ -1184,12 +1219,12 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1">
         <v>0.69</v>
@@ -1201,12 +1236,12 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1">
         <v>0.64</v>
@@ -1218,12 +1253,12 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1">
         <v>0.64</v>
@@ -1235,12 +1270,12 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1">
         <v>0.67</v>
@@ -1252,12 +1287,12 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C11" s="1">
         <v>0.64</v>
@@ -1269,12 +1304,12 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>0.64</v>
@@ -1286,12 +1321,12 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C13" s="1">
         <v>0.72</v>
@@ -1303,12 +1338,12 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C14" s="1">
         <v>0.67</v>
@@ -1320,12 +1355,12 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C15" s="1">
         <v>0.63</v>
@@ -1337,12 +1372,12 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1">
         <v>0.64</v>
@@ -1359,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C17" s="1">
         <v>0.67</v>
@@ -1376,7 +1411,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1">
         <v>0.66</v>
@@ -1393,7 +1428,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C19" s="1">
         <v>0.65</v>
@@ -1410,7 +1445,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C20" s="1">
         <v>0.67</v>
@@ -1427,7 +1462,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C21" s="1">
         <v>0.69</v>
@@ -1444,7 +1479,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C22" s="1">
         <v>0.62</v>
@@ -1461,7 +1496,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C23" s="1">
         <v>0.61</v>
@@ -1478,7 +1513,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C24" s="1">
         <v>0.67</v>
@@ -1495,7 +1530,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C25" s="1">
         <v>0.68</v>
@@ -1512,7 +1547,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C26" s="1">
         <v>0.69</v>
@@ -1529,7 +1564,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C27" s="1">
         <v>0.68</v>
@@ -1546,7 +1581,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C28" s="1">
         <v>0.74</v>
@@ -1563,7 +1598,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C29" s="1">
         <v>0.69</v>
@@ -1580,7 +1615,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C30" s="1">
         <v>0.68</v>
@@ -1597,7 +1632,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C31" s="1">
         <v>0.66</v>
@@ -1614,7 +1649,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C32" s="1">
         <v>0.62</v>
@@ -1631,7 +1666,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C33" s="1">
         <v>0.67</v>
@@ -1648,7 +1683,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C34" s="1">
         <v>0.64</v>
@@ -1665,7 +1700,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C35" s="1">
         <v>0.62</v>
@@ -1682,7 +1717,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C36" s="1">
         <v>0.7</v>
@@ -1699,7 +1734,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C37" s="1">
         <v>0.64</v>
@@ -1716,7 +1751,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C38" s="1">
         <v>0.69</v>
@@ -1733,7 +1768,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C39" s="1">
         <v>0.69</v>
@@ -1750,7 +1785,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C40" s="1">
         <v>0.63</v>
@@ -1767,7 +1802,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1">
         <v>0.65</v>
@@ -1784,7 +1819,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C42" s="1">
         <v>0.66</v>
@@ -1801,7 +1836,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C43" s="1">
         <v>0.76</v>
@@ -1818,7 +1853,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C44" s="1">
         <v>0.66</v>
@@ -1835,7 +1870,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C45" s="1">
         <v>0.66</v>
@@ -1852,7 +1887,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C46" s="1">
         <v>0.65</v>
@@ -1869,7 +1904,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C47" s="1">
         <v>0.69</v>
@@ -1886,7 +1921,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C48" s="1">
         <v>0.63</v>
@@ -1903,7 +1938,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C49" s="1">
         <v>0.69</v>
@@ -1920,7 +1955,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C50" s="1">
         <v>0.64</v>
@@ -1937,7 +1972,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C51" s="1">
         <v>0.67</v>
@@ -1954,7 +1989,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C52" s="1">
         <v>0.72</v>
@@ -1968,6 +2003,648 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{0B8F27B7-5721-4573-9A96-65F89E45E681}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71DCFFD5-5F65-4626-8979-D4600789D01E}">
+  <dimension ref="A1:AZ4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" t="s">
+        <v>5</v>
+      </c>
+      <c r="T1" t="s">
+        <v>35</v>
+      </c>
+      <c r="U1" t="s">
+        <v>45</v>
+      </c>
+      <c r="V1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="S2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="V2" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="W2" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="X2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="AU2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="AW2" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="AX2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="AY2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="AZ2" s="1">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="U3" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="V3" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="X3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AR3" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="AS3" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="AT3" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="AU3" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="AV3" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="AW3" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="AX3" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="AY3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="AZ3" s="1">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="V4" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="X4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AP4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="AQ4" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AR4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="AS4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AT4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AU4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AV4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AW4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AX4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AY4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AZ4" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
